--- a/materials/04_rg_intervention_framework/asb_framework_04_3_framework_to_architecture_translation.xlsx
+++ b/materials/04_rg_intervention_framework/asb_framework_04_3_framework_to_architecture_translation.xlsx
@@ -1636,12 +1636,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Empirically Tested prioritised; convergent evidence set tools especially favoured. Architecture-deployed Library tools show convergent over-representation: 50% of Architecture-drawn tools have ≥1 convergent paper in Taxonomy Source vs. 30.5% of full Library; among Empirically tested Architecture-drawn tools, 61% have convergent evidence vs. 44.8% Library baseline.</t>
+          <t>Empirically Tested prioritised; convergent evidence set tools especially favoured. Architecture-deployed Library tools show convergent over-representation: 36.2% of Architecture-drawn tools have ≥1 convergent paper in Taxonomy Source vs. 22.4% of full Library; among Empirically tested Architecture-drawn tools, 46.3% have convergent evidence vs. 30.8% Library baseline.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Library's Evidence Status drives selection priority. The architecture is heavily weighted toward Empirically tested tier and especially convergent-set tools. Among the 58 unique Library tools the architecture draws on, 41 are Empirically tested (70.7%) and 29 (50.0%) have convergent-set evidence — substantially higher than Library baseline rates of 68.1% Empirically tested and 30.5% convergent-set. This over-representation is the strongest demonstration of the architecture's evidence-based selection logic. Extrapolated Library tools appear in the architecture only where they fill operationally necessary gaps: T177 (Failed Deposit Counter), T178 (Withdrawal Reversal Friction), T180 (Post-Win Withdrawal), T184 (Post-Loss Session Re-Entry Delay).</t>
+          <t>Library's Evidence Status drives selection priority. The architecture is heavily weighted toward Empirically tested tier and especially convergent-set tools. Among the 58 unique Library tools the architecture draws on, 41 are Empirically tested (70.7%) and 21 (36.2%) have convergent-set evidence — substantially higher than Library baseline rates of 68.1% Empirically tested and 22.4% convergent-set. This over-representation is the strongest demonstration of the architecture's evidence-based selection logic. Extrapolated Library tools appear in the architecture only where they fill operationally necessary gaps: T177 (Failed Deposit Counter), T178 (Withdrawal Reversal Friction), T180 (Post-Win Withdrawal), T184 (Post-Loss Session Re-Entry Delay).</t>
         </is>
       </c>
     </row>
@@ -1967,11 +1967,7 @@
           <t>Policy / structural</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E8" s="12" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2292,11 +2288,7 @@
           <t>Policy / structural</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E15" s="12" t="n"/>
       <c r="F15" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -2339,11 +2331,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E16" s="12" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1.10</t>
@@ -2386,11 +2374,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E17" s="12" t="n"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
           <t>1.10</t>
@@ -2433,11 +2417,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E18" s="12" t="n"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1.10</t>
@@ -2566,11 +2546,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E21" s="12" t="n"/>
       <c r="F21" s="6" t="inlineStr">
         <is>
           <t>1.11</t>
@@ -2922,11 +2898,7 @@
           <t>Theoretically derived</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E29" s="12" t="n"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -4886,11 +4858,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E73" s="12" t="n"/>
       <c r="F73" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -5606,11 +5574,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E89" s="12" t="n"/>
       <c r="F89" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -5841,11 +5805,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E94" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E94" s="12" t="n"/>
       <c r="F94" s="4" t="inlineStr">
         <is>
           <t>—</t>
@@ -5931,11 +5891,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E96" s="12" t="n"/>
       <c r="F96" s="4" t="inlineStr">
         <is>
           <t>—</t>
@@ -6107,11 +6063,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E100" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E100" s="12" t="n"/>
       <c r="F100" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -6283,11 +6235,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E104" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E104" s="12" t="n"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
           <t>—</t>
@@ -7867,11 +7815,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E140" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E140" s="12" t="n"/>
       <c r="F140" s="4" t="inlineStr">
         <is>
           <t>—</t>
@@ -7914,11 +7858,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E141" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E141" s="12" t="n"/>
       <c r="F141" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -7961,11 +7901,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E142" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E142" s="12" t="n"/>
       <c r="F142" s="4" t="inlineStr">
         <is>
           <t>—</t>
@@ -9212,11 +9148,7 @@
           <t>Empirically tested</t>
         </is>
       </c>
-      <c r="E171" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E171" s="12" t="n"/>
       <c r="F171" s="6" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -11251,8 +11183,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
@@ -11354,8 +11284,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
@@ -11655,8 +11583,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
@@ -11786,8 +11712,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
@@ -11835,12 +11759,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Of 210 Library tools, 64 have ≥1 convergent paper in Taxonomy Source</t>
+          <t>Of 210 Library tools, 47 have ≥1 convergent paper in Taxonomy Source</t>
         </is>
       </c>
     </row>
@@ -11855,12 +11779,12 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Of 143 Empirically tested tools, 64 have convergent evidence — convergent-set is concentrated in evidenced tier</t>
+          <t>Of 143 Empirically tested tools, 44 have convergent evidence — convergent-set is concentrated in evidenced tier</t>
         </is>
       </c>
     </row>
@@ -11875,12 +11799,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Of 58 Library tools the architecture draws on, 29 have convergent evidence — substantially above the Library baseline of 30.5%</t>
+          <t>Of 58 Library tools the architecture draws on, 21 have convergent evidence — substantially above the Library baseline of 22.4%</t>
         </is>
       </c>
     </row>
@@ -11895,17 +11819,15 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Among the 41 Empirically tested tools the architecture draws on, 25 (61.0%) have convergent evidence — above the Library baseline rate of 44.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58"/>
+          <t>Among the 41 Empirically tested tools the architecture draws on, 19 (46.3%) have convergent evidence — above the Library baseline rate of 30.8%</t>
+        </is>
+      </c>
+    </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
@@ -11951,7 +11873,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>7/9</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11893,7 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12053,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>0/4</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12073,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12093,7 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12153,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>0/3</t>
         </is>
       </c>
     </row>
